--- a/data tables.xlsx
+++ b/data tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://1651wilkening-my.sharepoint.com/personal/canyon_white_convergint_com/Documents/Documents/GitHub/DATA 3010 Python Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{417E2773-B8DC-4323-9829-AEC885D3D4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{417E2773-B8DC-4323-9829-AEC885D3D4C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC947A67-6166-496A-8645-0F7753B8C8BC}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{76651B23-9EEE-4685-BE34-E17753E32416}"/>
+    <workbookView minimized="1" xWindow="35100" yWindow="4290" windowWidth="16410" windowHeight="11295" activeTab="1" xr2:uid="{76651B23-9EEE-4685-BE34-E17753E32416}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="53">
   <si>
     <t>Univariate Frequency Table for Degree</t>
   </si>
@@ -196,9 +196,6 @@
   </si>
   <si>
     <t>Count</t>
-  </si>
-  <si>
-    <t>65-44</t>
   </si>
   <si>
     <t>Stratified Analysis for Means of tvhours and chldidel by AgeRange</t>
@@ -434,13 +431,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -465,122 +459,122 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -922,180 +916,180 @@
   <sheetFormatPr defaultColWidth="12.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="2" t="s">
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="I1" s="2" t="s">
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="I1" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>52</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>13.1</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="4">
         <v>139</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>35.01</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="4">
         <v>294</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="6">
         <v>74.06</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>30</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>7.56</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="4">
         <v>137</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="6">
         <v>34.51</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="4">
         <v>103</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="6">
         <v>25.94</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>231</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>58.19</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="4">
         <v>8</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="6">
         <v>2.02</v>
       </c>
-      <c r="I6" s="6"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="7"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="6"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>28</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>7.05</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="4">
         <v>113</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="6">
         <v>28.46</v>
       </c>
-      <c r="I7" s="6"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="7"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="6"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>56</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>14.11</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="7"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="7"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="6"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="6"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="6"/>
+      <c r="A10" s="5"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
+      <c r="A12" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1118,439 +1112,439 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="31"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="43"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="22" t="s">
+      <c r="C3" s="45"/>
+      <c r="D3" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="17"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="12"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="16">
         <v>230</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="16">
         <v>27</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="9">
         <f>D5+E5</f>
         <v>257</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="15"/>
-      <c r="C6" s="23" t="s">
+      <c r="B6" s="48"/>
+      <c r="C6" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="17">
         <v>0.89500000000000002</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="17">
         <v>0.105</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="10">
         <f>D6+E6</f>
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="19">
         <v>97</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="19">
         <v>43</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="9">
         <f>D7+E7</f>
         <v>140</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="15"/>
-      <c r="C8" s="23" t="s">
+      <c r="B8" s="48"/>
+      <c r="C8" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="17">
         <v>0.69299999999999995</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="17">
         <v>0.307</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="10">
         <f>D8+E8</f>
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="20">
         <f>D5+D7</f>
         <v>327</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="20">
         <f>E5+E7</f>
         <v>70</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="21">
         <f>D9+E9</f>
         <v>397</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="40"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="C12" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="41" t="s">
+      <c r="D12" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="35" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="16"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="12"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="36"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="6">
         <v>2.08</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>48.48</v>
       </c>
-      <c r="E14" s="38">
+      <c r="E14" s="25">
         <v>2.25</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="6">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="6">
         <v>52.2</v>
       </c>
-      <c r="E15" s="38">
+      <c r="E15" s="25">
         <v>2.4700000000000002</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="6">
         <v>3.42</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="6">
         <v>43.67</v>
       </c>
-      <c r="E16" s="38">
+      <c r="E16" s="25">
         <v>2.56</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="6">
         <v>2.29</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="6">
         <v>43.61</v>
       </c>
-      <c r="E17" s="38">
+      <c r="E17" s="25">
         <v>2.21</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="22">
         <v>3.61</v>
       </c>
-      <c r="D18" s="36">
+      <c r="D18" s="23">
         <v>53.91</v>
       </c>
-      <c r="E18" s="39">
+      <c r="E18" s="26">
         <v>2.73</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="43" t="s">
+      <c r="C23" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="41" t="s">
+      <c r="D23" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="E23" s="41" t="s">
+      <c r="E23" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="F23" s="41" t="s">
+      <c r="F23" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="G23" s="41" t="s">
+      <c r="G23" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="H23" s="41" t="s">
+      <c r="H23" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="I23" s="13" t="s">
+      <c r="I23" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="16"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="12"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="36"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="4">
         <v>0</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="4">
         <v>6</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="4">
         <v>2</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="4">
         <v>52</v>
       </c>
-      <c r="G25" s="7">
+      <c r="G25" s="6">
         <v>2.08</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="4">
         <v>1.19</v>
       </c>
-      <c r="I25" s="46">
+      <c r="I25" s="28">
         <v>2</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="4">
         <v>0</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="4">
         <v>8</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="4">
         <v>2</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="4">
         <v>30</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="6">
         <v>2.2000000000000002</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="4">
         <v>1.58</v>
       </c>
-      <c r="I26" s="46">
+      <c r="I26" s="28">
         <v>2</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="4">
         <v>0</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="4">
         <v>20</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="4">
         <v>3</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="4">
         <v>231</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G27" s="6">
         <v>3.42</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="4">
         <v>2.42</v>
       </c>
-      <c r="I27" s="46">
+      <c r="I27" s="28">
         <v>2</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="4">
         <v>0</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="4">
         <v>12</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="4">
         <v>2</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="4">
         <v>28</v>
       </c>
-      <c r="G28" s="7">
+      <c r="G28" s="6">
         <v>2.29</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="4">
         <v>2.21</v>
       </c>
-      <c r="I28" s="46">
+      <c r="I28" s="28">
         <v>2</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="47">
+      <c r="C29" s="29">
         <v>0</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="8">
         <v>22</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="8">
         <v>3</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="8">
         <v>56</v>
       </c>
-      <c r="G29" s="36">
+      <c r="G29" s="23">
         <v>3.61</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="8">
         <v>3.54</v>
       </c>
-      <c r="I29" s="37">
+      <c r="I29" s="24">
         <v>4</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B32" s="48" t="s">
+      <c r="B32" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="C32" s="48"/>
+      <c r="C32" s="32"/>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="49" t="s">
+      <c r="B33" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="49"/>
+      <c r="C33" s="31"/>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="49"/>
-      <c r="C34" s="49"/>
+      <c r="B34" s="31"/>
+      <c r="C34" s="31"/>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="50" t="s">
+      <c r="B36" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="C36" s="50"/>
+      <c r="C36" s="32"/>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="49" t="s">
+      <c r="B37" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="49"/>
+      <c r="C37" s="31"/>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="49"/>
-      <c r="C38" s="49"/>
+      <c r="B38" s="31"/>
+      <c r="C38" s="31"/>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B40" s="50" t="s">
+      <c r="B40" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="C40" s="50"/>
+      <c r="C40" s="32"/>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B41" s="49" t="s">
+      <c r="B41" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="49"/>
+      <c r="C41" s="31"/>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="49"/>
-      <c r="C42" s="49"/>
+      <c r="B42" s="31"/>
+      <c r="C42" s="31"/>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
@@ -1610,106 +1604,102 @@
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B62" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="C62" s="50"/>
-      <c r="D62" s="50"/>
+      <c r="B62" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="C62" s="32"/>
+      <c r="D62" s="32"/>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B63" s="14" t="s">
+      <c r="B63" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="C63" s="43" t="s">
+      <c r="C63" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="D63" s="13" t="s">
+      <c r="D63" s="35" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B64" s="16"/>
-      <c r="C64" s="44"/>
-      <c r="D64" s="12"/>
+      <c r="B64" s="38"/>
+      <c r="C64" s="34"/>
+      <c r="D64" s="36"/>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B65" s="27" t="s">
+      <c r="B65" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C65" s="7">
+      <c r="C65" s="6">
         <v>3.3</v>
       </c>
-      <c r="D65" s="51">
+      <c r="D65" s="30">
         <v>2.64</v>
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B66" s="27" t="s">
+      <c r="B66" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C66" s="7">
+      <c r="C66" s="6">
         <v>2.88</v>
       </c>
-      <c r="D66" s="46">
+      <c r="D66" s="28">
         <v>2.33</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B67" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C67" s="7">
+      <c r="B67" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C67" s="6">
         <v>2.69</v>
       </c>
-      <c r="D67" s="46">
+      <c r="D67" s="28">
         <v>2.38</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B68" s="27" t="s">
+      <c r="B68" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C68" s="7">
+      <c r="C68" s="6">
         <v>2.9</v>
       </c>
-      <c r="D68" s="46">
+      <c r="D68" s="28">
         <v>2.4300000000000002</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B69" s="27" t="s">
+      <c r="B69" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C69" s="7">
+      <c r="C69" s="6">
         <v>3.24</v>
       </c>
-      <c r="D69" s="46">
+      <c r="D69" s="28">
         <v>2.4500000000000002</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B70" s="23" t="s">
+      <c r="B70" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C70" s="35">
+      <c r="C70" s="22">
         <v>3.69</v>
       </c>
-      <c r="D70" s="37">
+      <c r="D70" s="24">
         <v>2.87</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B37:C38"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C42"/>
-    <mergeCell ref="C63:C64"/>
-    <mergeCell ref="D63:D64"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="H23:H24"/>
     <mergeCell ref="I23:I24"/>
     <mergeCell ref="B32:C32"/>
@@ -1722,13 +1712,18 @@
     <mergeCell ref="C23:C24"/>
     <mergeCell ref="D23:D24"/>
     <mergeCell ref="E23:E24"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="D63:D64"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="B37:C38"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C42"/>
+    <mergeCell ref="C63:C64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>